--- a/ig/nr-add-sato2-profile/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/ig/nr-add-sato2-profile/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:40:40+00:00</t>
+    <t>2023-11-23T10:07:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
